--- a/formato.xlsx
+++ b/formato.xlsx
@@ -3,21 +3,21 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3690" yWindow="4215" windowWidth="21600" windowHeight="11385" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3300" yWindow="2745" windowWidth="21600" windowHeight="11385" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Table 2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="14">
     <font>
       <name val="Times New Roman"/>
       <charset val="204"/>
@@ -50,6 +50,54 @@
       <i val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="1"/>
+      <b val="1"/>
+      <i val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="1"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="1"/>
+      <b val="1"/>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="1"/>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="1"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -239,7 +287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="158">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -270,8 +318,356 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="22"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="15"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="15"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="15"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -279,121 +675,72 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="22"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="15"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -469,6 +816,83 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>254634</colOff>
+      <row>1</row>
+      <rowOff>18568</rowOff>
+    </from>
+    <ext cx="190500" cy="123825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="image1.png"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="190500" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>254634</colOff>
+      <row>2</row>
+      <rowOff>23448</rowOff>
+    </from>
+    <ext cx="190500" cy="123825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="image1.png"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="190500" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -765,632 +1189,594 @@
   <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="12.75"/>
   <cols>
-    <col width="15.5" customWidth="1" style="19" min="1" max="1"/>
-    <col width="7.5" customWidth="1" style="19" min="2" max="2"/>
-    <col width="4" customWidth="1" style="19" min="3" max="3"/>
-    <col width="8" customWidth="1" style="19" min="4" max="4"/>
-    <col width="2.6640625" customWidth="1" style="19" min="5" max="5"/>
-    <col width="8.83203125" customWidth="1" style="19" min="6" max="6"/>
-    <col width="4" customWidth="1" style="19" min="7" max="7"/>
-    <col width="3.5" customWidth="1" style="19" min="8" max="8"/>
-    <col width="13.1640625" customWidth="1" style="19" min="9" max="9"/>
-    <col width="10.83203125" customWidth="1" style="19" min="10" max="10"/>
-    <col width="3.5" customWidth="1" style="19" min="11" max="11"/>
-    <col width="9.83203125" customWidth="1" style="19" min="12" max="12"/>
-    <col width="9.5" customWidth="1" style="19" min="13" max="13"/>
-    <col width="2.83203125" customWidth="1" style="19" min="14" max="14"/>
+    <col width="15.5" customWidth="1" style="126" min="1" max="1"/>
+    <col width="7.5" customWidth="1" style="126" min="2" max="2"/>
+    <col width="4" customWidth="1" style="126" min="3" max="3"/>
+    <col width="8" customWidth="1" style="126" min="4" max="4"/>
+    <col width="2.6640625" customWidth="1" style="126" min="5" max="5"/>
+    <col width="8.83203125" customWidth="1" style="126" min="6" max="6"/>
+    <col width="4" customWidth="1" style="126" min="7" max="7"/>
+    <col width="3.5" customWidth="1" style="126" min="8" max="8"/>
+    <col width="13.1640625" customWidth="1" style="126" min="9" max="9"/>
+    <col width="10.83203125" customWidth="1" style="126" min="10" max="10"/>
+    <col width="3.5" customWidth="1" style="126" min="11" max="11"/>
+    <col width="9.83203125" customWidth="1" style="126" min="12" max="12"/>
+    <col width="9.5" customWidth="1" style="126" min="13" max="13"/>
+    <col width="2.83203125" customWidth="1" style="126" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" s="19">
-      <c r="A1" s="18" t="inlineStr">
+    <row r="1" ht="21" customHeight="1" s="126">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>1.  INFORMACIÓN GENERAL</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18.95" customHeight="1" s="19">
-      <c r="A2" s="11" t="inlineStr">
+    <row r="2" ht="18.95" customHeight="1" s="126">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Regional:</t>
         </is>
       </c>
-      <c r="B2" s="22" t="inlineStr">
+      <c r="B2" s="127" t="inlineStr">
         <is>
           <t>BARRANCABERMEJA</t>
         </is>
       </c>
-      <c r="C2" s="12" t="n"/>
-      <c r="D2" s="12" t="n"/>
-      <c r="E2" s="12" t="n"/>
-      <c r="F2" s="13" t="n"/>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="C2" s="128" t="n"/>
+      <c r="D2" s="128" t="n"/>
+      <c r="E2" s="128" t="n"/>
+      <c r="F2" s="129" t="n"/>
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Centro de Formación:</t>
         </is>
       </c>
-      <c r="H2" s="12" t="n"/>
-      <c r="I2" s="13" t="n"/>
-      <c r="J2" s="16" t="inlineStr">
+      <c r="H2" s="128" t="n"/>
+      <c r="I2" s="129" t="n"/>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>CENTRO INDUSTRIAL Y DEL DESARROLLO TECNOLOGICO</t>
         </is>
       </c>
-      <c r="K2" s="12" t="n"/>
-      <c r="L2" s="12" t="n"/>
-      <c r="M2" s="13" t="n"/>
-    </row>
-    <row r="3" ht="20.1" customHeight="1" s="19">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="K2" s="128" t="n"/>
+      <c r="L2" s="128" t="n"/>
+      <c r="M2" s="129" t="n"/>
+    </row>
+    <row r="3" ht="20.1" customHeight="1" s="126">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Programa de Formación:</t>
         </is>
       </c>
-      <c r="B3" s="12" t="n"/>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="B3" s="128" t="n"/>
+      <c r="C3" s="129" t="n"/>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>INTEGRACION DE CONTENIDOS DIGITALES.</t>
         </is>
       </c>
-      <c r="E3" s="12" t="n"/>
-      <c r="F3" s="12" t="n"/>
-      <c r="G3" s="12" t="n"/>
-      <c r="H3" s="12" t="n"/>
-      <c r="I3" s="13" t="n"/>
-      <c r="J3" s="14" t="inlineStr">
+      <c r="E3" s="128" t="n"/>
+      <c r="F3" s="128" t="n"/>
+      <c r="G3" s="128" t="n"/>
+      <c r="H3" s="128" t="n"/>
+      <c r="I3" s="129" t="n"/>
+      <c r="J3" s="130" t="inlineStr">
         <is>
           <t>No. de Ficha:</t>
         </is>
       </c>
-      <c r="K3" s="13" t="n"/>
-      <c r="L3" s="15" t="n">
+      <c r="K3" s="129" t="n"/>
+      <c r="L3" s="3" t="n">
         <v>5050505</v>
       </c>
-      <c r="M3" s="13" t="n"/>
-    </row>
-    <row r="4" ht="12" customHeight="1" s="19">
-      <c r="A4" s="16" t="n"/>
-      <c r="B4" s="12" t="n"/>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="12" t="n"/>
-      <c r="G4" s="12" t="n"/>
-      <c r="H4" s="12" t="n"/>
-      <c r="I4" s="12" t="n"/>
-      <c r="J4" s="12" t="n"/>
-      <c r="K4" s="12" t="n"/>
-      <c r="L4" s="12" t="n"/>
-      <c r="M4" s="13" t="n"/>
-    </row>
-    <row r="5" ht="13.5" customHeight="1" s="19">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="M3" s="129" t="n"/>
+    </row>
+    <row r="4" ht="12" customHeight="1" s="126">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="128" t="n"/>
+      <c r="C4" s="128" t="n"/>
+      <c r="D4" s="128" t="n"/>
+      <c r="E4" s="128" t="n"/>
+      <c r="F4" s="128" t="n"/>
+      <c r="G4" s="128" t="n"/>
+      <c r="H4" s="128" t="n"/>
+      <c r="I4" s="128" t="n"/>
+      <c r="J4" s="128" t="n"/>
+      <c r="K4" s="128" t="n"/>
+      <c r="L4" s="128" t="n"/>
+      <c r="M4" s="129" t="n"/>
+    </row>
+    <row r="5" ht="13.5" customHeight="1" s="126">
+      <c r="A5" s="131" t="inlineStr">
         <is>
           <t>Datos del Aprendiz</t>
         </is>
       </c>
-      <c r="B5" s="21" t="n"/>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="B5" s="132" t="n"/>
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="D5" s="128" t="n"/>
+      <c r="E5" s="129" t="n"/>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>CARLOS DAVID ACUÑA MORENO</t>
         </is>
       </c>
-      <c r="G5" s="12" t="n"/>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
-      <c r="M5" s="13" t="n"/>
-    </row>
-    <row r="6" ht="13.5" customHeight="1" s="19">
-      <c r="A6" s="26" t="n"/>
-      <c r="B6" s="27" t="n"/>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="G5" s="128" t="n"/>
+      <c r="H5" s="128" t="n"/>
+      <c r="I5" s="128" t="n"/>
+      <c r="J5" s="128" t="n"/>
+      <c r="K5" s="128" t="n"/>
+      <c r="L5" s="128" t="n"/>
+      <c r="M5" s="129" t="n"/>
+    </row>
+    <row r="6" ht="13.5" customHeight="1" s="126">
+      <c r="A6" s="133" t="n"/>
+      <c r="B6" s="134" t="n"/>
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>Identificación:</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="D6" s="128" t="n"/>
+      <c r="E6" s="129" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>1005190289</t>
         </is>
       </c>
-      <c r="G6" s="12" t="n"/>
-      <c r="H6" s="12" t="n"/>
-      <c r="I6" s="12" t="n"/>
-      <c r="J6" s="12" t="n"/>
-      <c r="K6" s="12" t="n"/>
-      <c r="L6" s="12" t="n"/>
-      <c r="M6" s="13" t="n"/>
-    </row>
-    <row r="7" ht="13.5" customHeight="1" s="19">
-      <c r="A7" s="26" t="n"/>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="G6" s="128" t="n"/>
+      <c r="H6" s="128" t="n"/>
+      <c r="I6" s="128" t="n"/>
+      <c r="J6" s="128" t="n"/>
+      <c r="K6" s="128" t="n"/>
+      <c r="L6" s="128" t="n"/>
+      <c r="M6" s="129" t="n"/>
+    </row>
+    <row r="7" ht="13.5" customHeight="1" s="126">
+      <c r="A7" s="133" t="n"/>
+      <c r="B7" s="134" t="n"/>
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>Teléfono:</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="D7" s="128" t="n"/>
+      <c r="E7" s="129" t="n"/>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Sin actualizar</t>
         </is>
       </c>
-      <c r="G7" s="12" t="n"/>
-      <c r="H7" s="12" t="n"/>
-      <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
-      <c r="M7" s="13" t="n"/>
-    </row>
-    <row r="8" ht="13.5" customHeight="1" s="19">
-      <c r="A8" s="26" t="n"/>
-      <c r="B8" s="27" t="n"/>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="G7" s="128" t="n"/>
+      <c r="H7" s="128" t="n"/>
+      <c r="I7" s="128" t="n"/>
+      <c r="J7" s="128" t="n"/>
+      <c r="K7" s="128" t="n"/>
+      <c r="L7" s="128" t="n"/>
+      <c r="M7" s="129" t="n"/>
+    </row>
+    <row r="8" ht="13.5" customHeight="1" s="126">
+      <c r="A8" s="133" t="n"/>
+      <c r="B8" s="134" t="n"/>
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>E-mail:</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="D8" s="128" t="n"/>
+      <c r="E8" s="129" t="n"/>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Sin actualizar</t>
         </is>
       </c>
-      <c r="G8" s="12" t="n"/>
-      <c r="H8" s="12" t="n"/>
-      <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="12" t="n"/>
-      <c r="M8" s="13" t="n"/>
-    </row>
-    <row r="9" ht="33.95" customHeight="1" s="19">
-      <c r="A9" s="28" t="n"/>
-      <c r="B9" s="29" t="n"/>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="G8" s="128" t="n"/>
+      <c r="H8" s="128" t="n"/>
+      <c r="I8" s="128" t="n"/>
+      <c r="J8" s="128" t="n"/>
+      <c r="K8" s="128" t="n"/>
+      <c r="L8" s="128" t="n"/>
+      <c r="M8" s="129" t="n"/>
+    </row>
+    <row r="9" ht="33.95" customHeight="1" s="126">
+      <c r="A9" s="135" t="n"/>
+      <c r="B9" s="136" t="n"/>
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>Alternativa registrada en SOFIA plus</t>
         </is>
       </c>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="D9" s="128" t="n"/>
+      <c r="E9" s="129" t="n"/>
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Contrato de aprendizaje</t>
         </is>
       </c>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
-      <c r="M9" s="13" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1" s="19">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="G9" s="128" t="n"/>
+      <c r="H9" s="128" t="n"/>
+      <c r="I9" s="128" t="n"/>
+      <c r="J9" s="128" t="n"/>
+      <c r="K9" s="128" t="n"/>
+      <c r="L9" s="128" t="n"/>
+      <c r="M9" s="129" t="n"/>
+    </row>
+    <row r="10" ht="27" customHeight="1" s="126">
+      <c r="A10" s="131" t="inlineStr">
         <is>
           <t>Ente Coformador</t>
         </is>
       </c>
-      <c r="B10" s="21" t="n"/>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="B10" s="132" t="n"/>
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Razón social
 Empresa:</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="D10" s="128" t="n"/>
+      <c r="E10" s="129" t="n"/>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" s="12" t="n"/>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="n"/>
-      <c r="M10" s="13" t="n"/>
-    </row>
-    <row r="11" ht="14.1" customHeight="1" s="19">
-      <c r="A11" s="26" t="n"/>
-      <c r="B11" s="27" t="n"/>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="G10" s="128" t="n"/>
+      <c r="H10" s="128" t="n"/>
+      <c r="I10" s="128" t="n"/>
+      <c r="J10" s="128" t="n"/>
+      <c r="K10" s="128" t="n"/>
+      <c r="L10" s="128" t="n"/>
+      <c r="M10" s="129" t="n"/>
+    </row>
+    <row r="11" ht="14.1" customHeight="1" s="126">
+      <c r="A11" s="133" t="n"/>
+      <c r="B11" s="134" t="n"/>
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>Nit:</t>
         </is>
       </c>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="D11" s="128" t="n"/>
+      <c r="E11" s="129" t="n"/>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="12" t="n"/>
-      <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="12" t="n"/>
-      <c r="M11" s="13" t="n"/>
-    </row>
-    <row r="12" ht="13.5" customHeight="1" s="19">
-      <c r="A12" s="26" t="n"/>
-      <c r="B12" s="27" t="n"/>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="G11" s="128" t="n"/>
+      <c r="H11" s="128" t="n"/>
+      <c r="I11" s="128" t="n"/>
+      <c r="J11" s="128" t="n"/>
+      <c r="K11" s="128" t="n"/>
+      <c r="L11" s="128" t="n"/>
+      <c r="M11" s="129" t="n"/>
+    </row>
+    <row r="12" ht="13.5" customHeight="1" s="126">
+      <c r="A12" s="133" t="n"/>
+      <c r="B12" s="134" t="n"/>
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>Dirección:</t>
         </is>
       </c>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="D12" s="128" t="n"/>
+      <c r="E12" s="129" t="n"/>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G12" s="12" t="n"/>
-      <c r="H12" s="12" t="n"/>
-      <c r="I12" s="12" t="n"/>
-      <c r="J12" s="12" t="n"/>
-      <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="n"/>
-      <c r="M12" s="13" t="n"/>
-    </row>
-    <row r="13" ht="45" customHeight="1" s="19">
-      <c r="A13" s="26" t="n"/>
-      <c r="B13" s="27" t="n"/>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="G12" s="128" t="n"/>
+      <c r="H12" s="128" t="n"/>
+      <c r="I12" s="128" t="n"/>
+      <c r="J12" s="128" t="n"/>
+      <c r="K12" s="128" t="n"/>
+      <c r="L12" s="128" t="n"/>
+      <c r="M12" s="129" t="n"/>
+    </row>
+    <row r="13" ht="45" customHeight="1" s="126">
+      <c r="A13" s="133" t="n"/>
+      <c r="B13" s="134" t="n"/>
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>Nombre del Jefe Inmediato del aprendiz:</t>
         </is>
       </c>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="24" t="inlineStr">
-        <is>
-          <t>sadsad</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="n"/>
-      <c r="H13" s="12" t="n"/>
-      <c r="I13" s="12" t="n"/>
-      <c r="J13" s="12" t="n"/>
-      <c r="K13" s="12" t="n"/>
-      <c r="L13" s="12" t="n"/>
-      <c r="M13" s="13" t="n"/>
-    </row>
-    <row r="14" ht="13.5" customHeight="1" s="19">
-      <c r="A14" s="26" t="n"/>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="D13" s="128" t="n"/>
+      <c r="E13" s="129" t="n"/>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>SDSADSA</t>
+        </is>
+      </c>
+      <c r="G13" s="128" t="n"/>
+      <c r="H13" s="128" t="n"/>
+      <c r="I13" s="128" t="n"/>
+      <c r="J13" s="128" t="n"/>
+      <c r="K13" s="128" t="n"/>
+      <c r="L13" s="128" t="n"/>
+      <c r="M13" s="129" t="n"/>
+    </row>
+    <row r="14" ht="13.5" customHeight="1" s="126">
+      <c r="A14" s="133" t="n"/>
+      <c r="B14" s="134" t="n"/>
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>sadsad</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="n"/>
-      <c r="H14" s="12" t="n"/>
-      <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
-      <c r="K14" s="12" t="n"/>
-      <c r="L14" s="12" t="n"/>
-      <c r="M14" s="13" t="n"/>
-    </row>
-    <row r="15" ht="14.1" customHeight="1" s="19">
-      <c r="A15" s="26" t="n"/>
-      <c r="B15" s="27" t="n"/>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="D14" s="128" t="n"/>
+      <c r="E14" s="129" t="n"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>DSADSA</t>
+        </is>
+      </c>
+      <c r="G14" s="128" t="n"/>
+      <c r="H14" s="128" t="n"/>
+      <c r="I14" s="128" t="n"/>
+      <c r="J14" s="128" t="n"/>
+      <c r="K14" s="128" t="n"/>
+      <c r="L14" s="128" t="n"/>
+      <c r="M14" s="129" t="n"/>
+    </row>
+    <row r="15" ht="14.1" customHeight="1" s="126">
+      <c r="A15" s="133" t="n"/>
+      <c r="B15" s="134" t="n"/>
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>Teléfono:</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>sadsa</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="12" t="n"/>
-      <c r="I15" s="12" t="n"/>
-      <c r="J15" s="12" t="n"/>
-      <c r="K15" s="12" t="n"/>
-      <c r="L15" s="12" t="n"/>
-      <c r="M15" s="13" t="n"/>
-    </row>
-    <row r="16" ht="13.5" customHeight="1" s="19">
-      <c r="A16" s="28" t="n"/>
-      <c r="B16" s="29" t="n"/>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="D15" s="128" t="n"/>
+      <c r="E15" s="129" t="n"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>DSADSA</t>
+        </is>
+      </c>
+      <c r="G15" s="128" t="n"/>
+      <c r="H15" s="128" t="n"/>
+      <c r="I15" s="128" t="n"/>
+      <c r="J15" s="128" t="n"/>
+      <c r="K15" s="128" t="n"/>
+      <c r="L15" s="128" t="n"/>
+      <c r="M15" s="129" t="n"/>
+    </row>
+    <row r="16" ht="13.5" customHeight="1" s="126">
+      <c r="A16" s="135" t="n"/>
+      <c r="B16" s="136" t="n"/>
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>E-mail:</t>
         </is>
       </c>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>ddfsjkdjskd@gmail.com</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="n"/>
-      <c r="H16" s="12" t="n"/>
-      <c r="I16" s="12" t="n"/>
-      <c r="J16" s="12" t="n"/>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="12" t="n"/>
-      <c r="M16" s="13" t="n"/>
-    </row>
-    <row r="17" ht="21" customHeight="1" s="19">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="D16" s="128" t="n"/>
+      <c r="E16" s="129" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="128" t="n"/>
+      <c r="H16" s="128" t="n"/>
+      <c r="I16" s="128" t="n"/>
+      <c r="J16" s="128" t="n"/>
+      <c r="K16" s="128" t="n"/>
+      <c r="L16" s="128" t="n"/>
+      <c r="M16" s="129" t="n"/>
+    </row>
+    <row r="17" ht="21" customHeight="1" s="126">
+      <c r="A17" s="137" t="inlineStr">
         <is>
           <t>2. PLANEACIÓN ETAPA PRODUCTIVA</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="12" t="n"/>
-      <c r="J17" s="12" t="n"/>
-      <c r="K17" s="12" t="n"/>
-      <c r="L17" s="12" t="n"/>
-      <c r="M17" s="13" t="n"/>
-    </row>
-    <row r="18" ht="18.95" customHeight="1" s="19">
-      <c r="A18" s="40" t="inlineStr">
+      <c r="B17" s="128" t="n"/>
+      <c r="C17" s="128" t="n"/>
+      <c r="D17" s="128" t="n"/>
+      <c r="E17" s="128" t="n"/>
+      <c r="F17" s="128" t="n"/>
+      <c r="G17" s="128" t="n"/>
+      <c r="H17" s="128" t="n"/>
+      <c r="I17" s="128" t="n"/>
+      <c r="J17" s="128" t="n"/>
+      <c r="K17" s="128" t="n"/>
+      <c r="L17" s="128" t="n"/>
+      <c r="M17" s="129" t="n"/>
+    </row>
+    <row r="18" ht="18.95" customHeight="1" s="126">
+      <c r="A18" s="138" t="inlineStr">
         <is>
           <t>CONCERTACIÓN PLAN DE TRABAJO DURANTE LA ETAPA PRODUCTIVA DEL APRENDIZ</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-      <c r="H18" s="12" t="n"/>
-      <c r="I18" s="12" t="n"/>
-      <c r="J18" s="12" t="n"/>
-      <c r="K18" s="12" t="n"/>
-      <c r="L18" s="12" t="n"/>
-      <c r="M18" s="13" t="n"/>
-    </row>
-    <row r="19" ht="23.1" customHeight="1" s="19">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="B18" s="128" t="n"/>
+      <c r="C18" s="128" t="n"/>
+      <c r="D18" s="128" t="n"/>
+      <c r="E18" s="128" t="n"/>
+      <c r="F18" s="128" t="n"/>
+      <c r="G18" s="128" t="n"/>
+      <c r="H18" s="128" t="n"/>
+      <c r="I18" s="128" t="n"/>
+      <c r="J18" s="128" t="n"/>
+      <c r="K18" s="128" t="n"/>
+      <c r="L18" s="128" t="n"/>
+      <c r="M18" s="129" t="n"/>
+    </row>
+    <row r="19" ht="23.1" customHeight="1" s="126">
+      <c r="A19" s="139" t="inlineStr">
         <is>
           <t>ACTIVIDADES A DESARROLLAR
 Relacione  las  actividades que el aprendiz va a realizar. (Estas    deben    corresponder    al    Perfil    del   egresado establecido    en   el   programa   de   formación   que   el</t>
         </is>
       </c>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
-      <c r="G19" s="21" t="n"/>
-      <c r="H19" s="41" t="inlineStr">
+      <c r="B19" s="140" t="n"/>
+      <c r="C19" s="140" t="n"/>
+      <c r="D19" s="140" t="n"/>
+      <c r="E19" s="140" t="n"/>
+      <c r="F19" s="140" t="n"/>
+      <c r="G19" s="132" t="n"/>
+      <c r="H19" s="141" t="inlineStr">
         <is>
           <t>EVIDENCIAS DE APRENDIZAJE</t>
         </is>
       </c>
-      <c r="I19" s="36" t="n"/>
-      <c r="J19" s="21" t="n"/>
-      <c r="K19" s="23" t="inlineStr">
+      <c r="I19" s="140" t="n"/>
+      <c r="J19" s="132" t="n"/>
+      <c r="K19" s="142" t="inlineStr">
         <is>
           <t>RECOLECCIÓN DE EVIDENCIAS</t>
         </is>
       </c>
-      <c r="L19" s="12" t="n"/>
-      <c r="M19" s="13" t="n"/>
-    </row>
-    <row r="20" ht="30.75" customHeight="1" s="19">
-      <c r="A20" s="26" t="n"/>
-      <c r="G20" s="27" t="n"/>
-      <c r="H20" s="26" t="n"/>
-      <c r="J20" s="27" t="n"/>
-      <c r="K20" s="20" t="inlineStr">
+      <c r="L19" s="128" t="n"/>
+      <c r="M19" s="129" t="n"/>
+    </row>
+    <row r="20" ht="30.75" customHeight="1" s="126">
+      <c r="A20" s="133" t="n"/>
+      <c r="G20" s="134" t="n"/>
+      <c r="H20" s="133" t="n"/>
+      <c r="J20" s="134" t="n"/>
+      <c r="K20" s="143" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="L20" s="21" t="n"/>
+      <c r="L20" s="132" t="n"/>
       <c r="M20" s="6" t="inlineStr">
         <is>
           <t>Lugar</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="13.5" customHeight="1" s="19">
-      <c r="A21" s="37" t="inlineStr">
+    <row r="21" ht="13.5" customHeight="1" s="126">
+      <c r="A21" s="144" t="inlineStr">
         <is>
           <t>aprendiz está desarrollando)</t>
         </is>
       </c>
-      <c r="B21" s="38" t="n"/>
-      <c r="C21" s="38" t="n"/>
-      <c r="D21" s="38" t="n"/>
-      <c r="E21" s="38" t="n"/>
-      <c r="F21" s="38" t="n"/>
-      <c r="G21" s="29" t="n"/>
-      <c r="H21" s="31" t="n"/>
-      <c r="I21" s="38" t="n"/>
-      <c r="J21" s="29" t="n"/>
-      <c r="K21" s="31" t="n"/>
-      <c r="L21" s="29" t="n"/>
-      <c r="M21" s="31" t="n"/>
-    </row>
-    <row r="22" ht="20.1" customHeight="1" s="19">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>sdasad</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="13" t="n"/>
-      <c r="H22" s="15" t="inlineStr">
+      <c r="B21" s="145" t="n"/>
+      <c r="C21" s="145" t="n"/>
+      <c r="D21" s="145" t="n"/>
+      <c r="E21" s="145" t="n"/>
+      <c r="F21" s="145" t="n"/>
+      <c r="G21" s="136" t="n"/>
+      <c r="H21" s="7" t="n"/>
+      <c r="I21" s="145" t="n"/>
+      <c r="J21" s="136" t="n"/>
+      <c r="K21" s="7" t="n"/>
+      <c r="L21" s="136" t="n"/>
+      <c r="M21" s="7" t="n"/>
+    </row>
+    <row r="22" ht="20.1" customHeight="1" s="126">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>sadsadsa</t>
         </is>
       </c>
-      <c r="I22" s="12" t="n"/>
-      <c r="J22" s="13" t="n"/>
-      <c r="K22" s="15" t="inlineStr">
-        <is>
-          <t>2024-04-18
+      <c r="B22" s="128" t="n"/>
+      <c r="C22" s="128" t="n"/>
+      <c r="D22" s="128" t="n"/>
+      <c r="E22" s="128" t="n"/>
+      <c r="F22" s="128" t="n"/>
+      <c r="G22" s="129" t="n"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>dsadsadsa</t>
+        </is>
+      </c>
+      <c r="I22" s="128" t="n"/>
+      <c r="J22" s="129" t="n"/>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>2024-04-05
 2024-05-02</t>
         </is>
       </c>
-      <c r="L22" s="13" t="n"/>
-      <c r="M22" s="15" t="inlineStr">
-        <is>
-          <t>dsadsa</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18.95" customHeight="1" s="19">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>dsadsadsa</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="12" t="n"/>
-      <c r="G23" s="13" t="n"/>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>dsadsadsa</t>
-        </is>
-      </c>
-      <c r="I23" s="12" t="n"/>
-      <c r="J23" s="13" t="n"/>
-      <c r="K23" s="16" t="inlineStr">
-        <is>
-          <t>2024-04-11
-2024-05-02</t>
-        </is>
-      </c>
-      <c r="L23" s="13" t="n"/>
-      <c r="M23" s="16" t="inlineStr">
-        <is>
-          <t>sadsadsa</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20.1" customHeight="1" s="19">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>dsadsad</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
-      <c r="G24" s="13" t="n"/>
-      <c r="H24" s="15" t="inlineStr">
-        <is>
-          <t>sadsadsadsa</t>
-        </is>
-      </c>
-      <c r="I24" s="12" t="n"/>
-      <c r="J24" s="13" t="n"/>
-      <c r="K24" s="15" t="inlineStr">
-        <is>
-          <t>2024-04-11
-2024-05-11</t>
-        </is>
-      </c>
-      <c r="L24" s="13" t="n"/>
-      <c r="M24" s="15" t="inlineStr">
-        <is>
-          <t>dsadsadsa</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="21.95" customHeight="1" s="19">
-      <c r="A25" s="32" t="inlineStr">
-        <is>
-          <t>OBSERVACIONES:</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="12" t="n"/>
-      <c r="F25" s="12" t="n"/>
-      <c r="G25" s="12" t="n"/>
-      <c r="H25" s="12" t="n"/>
-      <c r="I25" s="12" t="n"/>
-      <c r="J25" s="12" t="n"/>
-      <c r="K25" s="12" t="n"/>
-      <c r="L25" s="12" t="n"/>
-      <c r="M25" s="13" t="n"/>
-    </row>
-    <row r="26" ht="57.95" customHeight="1" s="19">
-      <c r="A26" s="39" t="inlineStr">
+      <c r="L22" s="129" t="n"/>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>sadasdsadsad</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18.95" customHeight="1" s="126">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="128" t="n"/>
+      <c r="C23" s="128" t="n"/>
+      <c r="D23" s="128" t="n"/>
+      <c r="E23" s="128" t="n"/>
+      <c r="F23" s="128" t="n"/>
+      <c r="G23" s="129" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="128" t="n"/>
+      <c r="J23" s="129" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="129" t="n"/>
+      <c r="M23" s="2" t="n"/>
+    </row>
+    <row r="24" ht="20.1" customHeight="1" s="126">
+      <c r="A24" s="3" t="n"/>
+      <c r="B24" s="128" t="n"/>
+      <c r="C24" s="128" t="n"/>
+      <c r="D24" s="128" t="n"/>
+      <c r="E24" s="128" t="n"/>
+      <c r="F24" s="128" t="n"/>
+      <c r="G24" s="129" t="n"/>
+      <c r="H24" s="3" t="n"/>
+      <c r="I24" s="128" t="n"/>
+      <c r="J24" s="129" t="n"/>
+      <c r="K24" s="3" t="n"/>
+      <c r="L24" s="129" t="n"/>
+      <c r="M24" s="3" t="n"/>
+    </row>
+    <row r="25" ht="21.95" customHeight="1" s="126">
+      <c r="A25" s="146" t="inlineStr">
+        <is>
+          <t>sadsadsadsad</t>
+        </is>
+      </c>
+      <c r="B25" s="128" t="n"/>
+      <c r="C25" s="128" t="n"/>
+      <c r="D25" s="128" t="n"/>
+      <c r="E25" s="128" t="n"/>
+      <c r="F25" s="128" t="n"/>
+      <c r="G25" s="128" t="n"/>
+      <c r="H25" s="128" t="n"/>
+      <c r="I25" s="128" t="n"/>
+      <c r="J25" s="128" t="n"/>
+      <c r="K25" s="128" t="n"/>
+      <c r="L25" s="128" t="n"/>
+      <c r="M25" s="129" t="n"/>
+    </row>
+    <row r="26" ht="57.95" customHeight="1" s="126">
+      <c r="A26" s="69" t="inlineStr">
         <is>
           <t>Nombre y Firma del ente Coformador</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="33" t="inlineStr">
+      <c r="B26" s="128" t="n"/>
+      <c r="C26" s="128" t="n"/>
+      <c r="D26" s="128" t="n"/>
+      <c r="E26" s="71" t="inlineStr">
         <is>
           <t>Firma del Aprendiz</t>
         </is>
       </c>
-      <c r="F26" s="12" t="n"/>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="12" t="n"/>
-      <c r="I26" s="30" t="inlineStr">
+      <c r="F26" s="128" t="n"/>
+      <c r="G26" s="128" t="n"/>
+      <c r="H26" s="128" t="n"/>
+      <c r="I26" s="73" t="inlineStr">
         <is>
           <t>Nombre y firma Instructor seguimiento</t>
         </is>
       </c>
-      <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
-      <c r="L26" s="12" t="n"/>
-      <c r="M26" s="13" t="n"/>
+      <c r="J26" s="128" t="n"/>
+      <c r="K26" s="128" t="n"/>
+      <c r="L26" s="128" t="n"/>
+      <c r="M26" s="129" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="57">
@@ -1400,20 +1786,20 @@
     <mergeCell ref="F11:M11"/>
     <mergeCell ref="A22:G22"/>
     <mergeCell ref="A17:M17"/>
+    <mergeCell ref="A10:B16"/>
+    <mergeCell ref="F10:M10"/>
+    <mergeCell ref="F16:M16"/>
     <mergeCell ref="A4:M4"/>
-    <mergeCell ref="F16:M16"/>
+    <mergeCell ref="F6:M6"/>
     <mergeCell ref="C9:E9"/>
-    <mergeCell ref="A10:B16"/>
+    <mergeCell ref="J2:M2"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="F10:M10"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="F6:M6"/>
     <mergeCell ref="C12:E12"/>
+    <mergeCell ref="A1:N1"/>
     <mergeCell ref="I26:M26"/>
     <mergeCell ref="F7:M7"/>
+    <mergeCell ref="K21:L21"/>
     <mergeCell ref="L3:M3"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="A1:N1"/>
     <mergeCell ref="C11:E11"/>
     <mergeCell ref="K20:L20"/>
     <mergeCell ref="F12:M12"/>
@@ -1457,7 +1843,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1465,708 +1851,712 @@
   <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="12.75"/>
   <cols>
-    <col width="1.1640625" customWidth="1" style="19" min="1" max="1"/>
-    <col width="17.83203125" customWidth="1" style="19" min="2" max="2"/>
-    <col width="5.5" customWidth="1" style="19" min="3" max="3"/>
-    <col width="5.83203125" customWidth="1" style="19" min="4" max="4"/>
-    <col width="12.83203125" customWidth="1" style="19" min="5" max="5"/>
-    <col width="1.83203125" customWidth="1" style="19" min="6" max="6"/>
-    <col width="10" customWidth="1" style="19" min="7" max="7"/>
-    <col width="8.6640625" customWidth="1" style="19" min="8" max="8"/>
-    <col width="3.33203125" customWidth="1" style="19" min="9" max="9"/>
-    <col width="10.83203125" customWidth="1" style="19" min="10" max="10"/>
-    <col width="9.83203125" customWidth="1" style="19" min="11" max="11"/>
-    <col width="6.6640625" customWidth="1" style="19" min="12" max="12"/>
-    <col width="7.5" customWidth="1" style="19" min="13" max="13"/>
+    <col width="1.1640625" customWidth="1" style="126" min="1" max="1"/>
+    <col width="17.83203125" customWidth="1" style="126" min="2" max="2"/>
+    <col width="5.5" customWidth="1" style="126" min="3" max="3"/>
+    <col width="5.83203125" customWidth="1" style="126" min="4" max="4"/>
+    <col width="12.83203125" customWidth="1" style="126" min="5" max="5"/>
+    <col width="1.83203125" customWidth="1" style="126" min="6" max="6"/>
+    <col width="10" customWidth="1" style="126" min="7" max="7"/>
+    <col width="8.6640625" customWidth="1" style="126" min="8" max="8"/>
+    <col width="3.33203125" customWidth="1" style="126" min="9" max="9"/>
+    <col width="10.83203125" customWidth="1" style="126" min="10" max="10"/>
+    <col width="9.83203125" customWidth="1" style="126" min="11" max="11"/>
+    <col width="6.6640625" customWidth="1" style="126" min="12" max="12"/>
+    <col width="7.5" customWidth="1" style="126" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" s="19">
-      <c r="A1" s="34" t="inlineStr">
+    <row r="1" ht="21" customHeight="1" s="126">
+      <c r="A1" s="137" t="inlineStr">
         <is>
           <t>3. SEGUIMIENTO ETAPA PRODUCTIVA</t>
         </is>
       </c>
-      <c r="B1" s="12" t="n"/>
-      <c r="C1" s="12" t="n"/>
-      <c r="D1" s="12" t="n"/>
-      <c r="E1" s="12" t="n"/>
-      <c r="F1" s="12" t="n"/>
-      <c r="G1" s="12" t="n"/>
-      <c r="H1" s="12" t="n"/>
-      <c r="I1" s="12" t="n"/>
-      <c r="J1" s="12" t="n"/>
-      <c r="K1" s="12" t="n"/>
-      <c r="L1" s="12" t="n"/>
-      <c r="M1" s="13" t="n"/>
-    </row>
-    <row r="2" ht="13.5" customHeight="1" s="19">
-      <c r="A2" s="47" t="inlineStr">
+      <c r="B1" s="128" t="n"/>
+      <c r="C1" s="128" t="n"/>
+      <c r="D1" s="128" t="n"/>
+      <c r="E1" s="128" t="n"/>
+      <c r="F1" s="128" t="n"/>
+      <c r="G1" s="128" t="n"/>
+      <c r="H1" s="128" t="n"/>
+      <c r="I1" s="128" t="n"/>
+      <c r="J1" s="128" t="n"/>
+      <c r="K1" s="128" t="n"/>
+      <c r="L1" s="128" t="n"/>
+      <c r="M1" s="129" t="n"/>
+    </row>
+    <row r="2" ht="13.5" customHeight="1" s="126">
+      <c r="A2" s="147" t="inlineStr">
         <is>
           <t>TIPO DE INFORME</t>
         </is>
       </c>
-      <c r="B2" s="36" t="n"/>
-      <c r="C2" s="21" t="n"/>
-      <c r="D2" s="22" t="inlineStr">
+      <c r="B2" s="140" t="n"/>
+      <c r="C2" s="132" t="n"/>
+      <c r="D2" s="127" t="inlineStr">
         <is>
           <t>PARCIAL   [X]</t>
         </is>
       </c>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="46" t="inlineStr">
+      <c r="E2" s="129" t="n"/>
+      <c r="F2" s="148" t="inlineStr">
         <is>
           <t>PERÍODO EVALUADO</t>
         </is>
       </c>
-      <c r="G2" s="36" t="n"/>
-      <c r="H2" s="36" t="n"/>
-      <c r="I2" s="21" t="n"/>
-      <c r="J2" s="22" t="inlineStr">
-        <is>
-          <t>Inicio:</t>
-        </is>
-      </c>
-      <c r="K2" s="12" t="n"/>
-      <c r="L2" s="12" t="n"/>
-      <c r="M2" s="13" t="n"/>
-    </row>
-    <row r="3" ht="14.1" customHeight="1" s="19">
-      <c r="A3" s="28" t="n"/>
-      <c r="B3" s="38" t="n"/>
-      <c r="C3" s="29" t="n"/>
-      <c r="D3" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FINAL    </t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="28" t="n"/>
-      <c r="G3" s="38" t="n"/>
-      <c r="H3" s="38" t="n"/>
-      <c r="I3" s="29" t="n"/>
-      <c r="J3" s="22" t="inlineStr">
-        <is>
-          <t>Finalización:</t>
-        </is>
-      </c>
-      <c r="K3" s="12" t="n"/>
-      <c r="L3" s="12" t="n"/>
-      <c r="M3" s="13" t="n"/>
-    </row>
-    <row r="4" ht="21.95" customHeight="1" s="19">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="G2" s="140" t="n"/>
+      <c r="H2" s="140" t="n"/>
+      <c r="I2" s="132" t="n"/>
+      <c r="J2" s="127" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="K2" s="128" t="n"/>
+      <c r="L2" s="128" t="n"/>
+      <c r="M2" s="129" t="n"/>
+    </row>
+    <row r="3" ht="14.1" customHeight="1" s="126">
+      <c r="A3" s="135" t="n"/>
+      <c r="B3" s="145" t="n"/>
+      <c r="C3" s="136" t="n"/>
+      <c r="D3" s="127" t="inlineStr">
+        <is>
+          <t>Final:</t>
+        </is>
+      </c>
+      <c r="E3" s="129" t="n"/>
+      <c r="F3" s="135" t="n"/>
+      <c r="G3" s="145" t="n"/>
+      <c r="H3" s="145" t="n"/>
+      <c r="I3" s="136" t="n"/>
+      <c r="J3" s="127" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="K3" s="128" t="n"/>
+      <c r="L3" s="128" t="n"/>
+      <c r="M3" s="129" t="n"/>
+    </row>
+    <row r="4" ht="21.95" customHeight="1" s="126">
+      <c r="A4" s="149" t="inlineStr">
         <is>
           <t>FACTORES ACTITUDINALES Y COMPORTAMENTALES</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n"/>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="12" t="n"/>
-      <c r="G4" s="12" t="n"/>
-      <c r="H4" s="12" t="n"/>
-      <c r="I4" s="12" t="n"/>
-      <c r="J4" s="12" t="n"/>
-      <c r="K4" s="12" t="n"/>
-      <c r="L4" s="12" t="n"/>
-      <c r="M4" s="13" t="n"/>
-    </row>
-    <row r="5" ht="14.1" customHeight="1" s="19">
-      <c r="A5" s="52" t="inlineStr">
+      <c r="B4" s="128" t="n"/>
+      <c r="C4" s="128" t="n"/>
+      <c r="D4" s="128" t="n"/>
+      <c r="E4" s="128" t="n"/>
+      <c r="F4" s="128" t="n"/>
+      <c r="G4" s="128" t="n"/>
+      <c r="H4" s="128" t="n"/>
+      <c r="I4" s="128" t="n"/>
+      <c r="J4" s="128" t="n"/>
+      <c r="K4" s="128" t="n"/>
+      <c r="L4" s="128" t="n"/>
+      <c r="M4" s="129" t="n"/>
+    </row>
+    <row r="5" ht="14.1" customHeight="1" s="126">
+      <c r="A5" s="150" t="inlineStr">
         <is>
           <t>VARIABLE</t>
         </is>
       </c>
-      <c r="B5" s="21" t="n"/>
-      <c r="C5" s="45" t="inlineStr">
+      <c r="B5" s="132" t="n"/>
+      <c r="C5" s="151" t="inlineStr">
         <is>
           <t>DESCRIPCIÓN</t>
         </is>
       </c>
-      <c r="D5" s="36" t="n"/>
-      <c r="E5" s="36" t="n"/>
-      <c r="F5" s="36" t="n"/>
-      <c r="G5" s="36" t="n"/>
-      <c r="H5" s="21" t="n"/>
-      <c r="I5" s="42" t="inlineStr">
+      <c r="D5" s="140" t="n"/>
+      <c r="E5" s="140" t="n"/>
+      <c r="F5" s="140" t="n"/>
+      <c r="G5" s="140" t="n"/>
+      <c r="H5" s="132" t="n"/>
+      <c r="I5" s="152" t="inlineStr">
         <is>
           <t>VALORACIÓN</t>
         </is>
       </c>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="13" t="n"/>
-      <c r="L5" s="44" t="inlineStr">
+      <c r="J5" s="128" t="n"/>
+      <c r="K5" s="129" t="n"/>
+      <c r="L5" s="153" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
-      <c r="M5" s="21" t="n"/>
-    </row>
-    <row r="6" ht="27" customHeight="1" s="19">
-      <c r="A6" s="28" t="n"/>
-      <c r="B6" s="29" t="n"/>
-      <c r="C6" s="28" t="n"/>
-      <c r="D6" s="38" t="n"/>
-      <c r="E6" s="38" t="n"/>
-      <c r="F6" s="38" t="n"/>
-      <c r="G6" s="38" t="n"/>
-      <c r="H6" s="29" t="n"/>
-      <c r="I6" s="47" t="inlineStr">
+      <c r="M5" s="132" t="n"/>
+    </row>
+    <row r="6" ht="27" customHeight="1" s="126">
+      <c r="A6" s="135" t="n"/>
+      <c r="B6" s="136" t="n"/>
+      <c r="C6" s="135" t="n"/>
+      <c r="D6" s="145" t="n"/>
+      <c r="E6" s="145" t="n"/>
+      <c r="F6" s="145" t="n"/>
+      <c r="G6" s="145" t="n"/>
+      <c r="H6" s="136" t="n"/>
+      <c r="I6" s="147" t="inlineStr">
         <is>
           <t>Satisfactorio</t>
         </is>
       </c>
-      <c r="J6" s="13" t="n"/>
-      <c r="K6" s="17" t="inlineStr">
+      <c r="J6" s="129" t="n"/>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>Por
 mejorar</t>
         </is>
       </c>
-      <c r="L6" s="28" t="n"/>
-      <c r="M6" s="29" t="n"/>
-    </row>
-    <row r="7" ht="54.95" customHeight="1" s="19">
-      <c r="A7" s="47" t="inlineStr">
+      <c r="L6" s="135" t="n"/>
+      <c r="M6" s="136" t="n"/>
+    </row>
+    <row r="7" ht="54.95" customHeight="1" s="126">
+      <c r="A7" s="147" t="inlineStr">
         <is>
           <t>RELACIONES INTERPERSONALES</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n"/>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="B7" s="129" t="n"/>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Desarrolla    relaciones   interpersonales   con   las personas   de   los   diferentes   niveles   del   ente Coformador  en  forma  armoniosa,  respetuosa  y enmarcada     dentro     de     los     principios     de
 convivencia social.</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
-      <c r="H7" s="13" t="n"/>
-      <c r="I7" s="24" t="n"/>
-      <c r="J7" s="13" t="n"/>
-      <c r="K7" s="24" t="n"/>
-      <c r="L7" s="24" t="n"/>
-      <c r="M7" s="13" t="n"/>
-    </row>
-    <row r="8" ht="33.95" customHeight="1" s="19">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="D7" s="128" t="n"/>
+      <c r="E7" s="128" t="n"/>
+      <c r="F7" s="128" t="n"/>
+      <c r="G7" s="128" t="n"/>
+      <c r="H7" s="129" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="129" t="n"/>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="129" t="n"/>
+    </row>
+    <row r="8" ht="33.95" customHeight="1" s="126">
+      <c r="A8" s="147" t="inlineStr">
         <is>
           <t>TRABAJO EN EQUIPO</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="B8" s="129" t="n"/>
+      <c r="C8" s="127" t="inlineStr">
         <is>
           <t>Participa    en    forma    activa    y   propositiva   en equipos   de   trabajo   asumiendo   los   roles,   de acuerdo con sus fortalezas.</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n"/>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="12" t="n"/>
-      <c r="G8" s="12" t="n"/>
-      <c r="H8" s="13" t="n"/>
-      <c r="I8" s="15" t="n"/>
-      <c r="J8" s="13" t="n"/>
-      <c r="K8" s="15" t="n"/>
-      <c r="L8" s="15" t="n"/>
-      <c r="M8" s="13" t="n"/>
-    </row>
-    <row r="9" ht="33.95" customHeight="1" s="19">
-      <c r="A9" s="47" t="inlineStr">
+      <c r="D8" s="128" t="n"/>
+      <c r="E8" s="128" t="n"/>
+      <c r="F8" s="128" t="n"/>
+      <c r="G8" s="128" t="n"/>
+      <c r="H8" s="129" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="129" t="n"/>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="129" t="n"/>
+    </row>
+    <row r="9" ht="33.95" customHeight="1" s="126">
+      <c r="A9" s="147" t="inlineStr">
         <is>
           <t>SOLUCIÓN DE PROBLEMAS</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="B9" s="129" t="n"/>
+      <c r="C9" s="127" t="inlineStr">
         <is>
           <t>Propone  alternativas  de  solución  a  situaciones problemáticas,  en  el  contexto  del  desarrollo  de su etapa productiva.</t>
         </is>
       </c>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="13" t="n"/>
-      <c r="I9" s="15" t="n"/>
-      <c r="J9" s="13" t="n"/>
-      <c r="K9" s="15" t="n"/>
-      <c r="L9" s="15" t="n"/>
-      <c r="M9" s="13" t="n"/>
-    </row>
-    <row r="10" ht="33" customHeight="1" s="19">
-      <c r="A10" s="55" t="inlineStr">
+      <c r="D9" s="128" t="n"/>
+      <c r="E9" s="128" t="n"/>
+      <c r="F9" s="128" t="n"/>
+      <c r="G9" s="128" t="n"/>
+      <c r="H9" s="129" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="129" t="n"/>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="129" t="n"/>
+    </row>
+    <row r="10" ht="33" customHeight="1" s="126">
+      <c r="A10" s="154" t="inlineStr">
         <is>
           <t>CUMPLIMIENTO</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="B10" s="129" t="n"/>
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Asume     compromiso     de     las     funciones     y responsabilidades  asignadas  en  el  desarrollo  de
 su trabajo.</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="12" t="n"/>
-      <c r="H10" s="13" t="n"/>
-      <c r="I10" s="15" t="n"/>
-      <c r="J10" s="13" t="n"/>
-      <c r="K10" s="15" t="n"/>
-      <c r="L10" s="15" t="n"/>
-      <c r="M10" s="13" t="n"/>
-    </row>
-    <row r="11" ht="45" customHeight="1" s="19">
-      <c r="A11" s="47" t="inlineStr">
+      <c r="D10" s="128" t="n"/>
+      <c r="E10" s="128" t="n"/>
+      <c r="F10" s="128" t="n"/>
+      <c r="G10" s="128" t="n"/>
+      <c r="H10" s="129" t="n"/>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="129" t="n"/>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="129" t="n"/>
+    </row>
+    <row r="11" ht="45" customHeight="1" s="126">
+      <c r="A11" s="147" t="inlineStr">
         <is>
           <t>ORGANIZACIÓN</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="B11" s="129" t="n"/>
+      <c r="C11" s="127" t="inlineStr">
         <is>
           <t>Demuestra capacidad para ordenar y disponer los elementos necesarios e información para facilitar la   ejecución  de  un  trabajo  y  el  logro  de  los objetivos.</t>
         </is>
       </c>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="13" t="n"/>
-      <c r="I11" s="24" t="n"/>
-      <c r="J11" s="13" t="n"/>
-      <c r="K11" s="24" t="n"/>
-      <c r="L11" s="24" t="n"/>
-      <c r="M11" s="13" t="n"/>
-    </row>
-    <row r="12" ht="18" customHeight="1" s="19">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="D11" s="128" t="n"/>
+      <c r="E11" s="128" t="n"/>
+      <c r="F11" s="128" t="n"/>
+      <c r="G11" s="128" t="n"/>
+      <c r="H11" s="129" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="129" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="129" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="126">
+      <c r="A12" s="149" t="inlineStr">
         <is>
           <t>FACTORES TÉCNICOS</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
-      <c r="H12" s="12" t="n"/>
-      <c r="I12" s="12" t="n"/>
-      <c r="J12" s="12" t="n"/>
-      <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="n"/>
-      <c r="M12" s="13" t="n"/>
-    </row>
-    <row r="13" ht="14.1" customHeight="1" s="19">
-      <c r="A13" s="52" t="inlineStr">
+      <c r="B12" s="128" t="n"/>
+      <c r="C12" s="128" t="n"/>
+      <c r="D12" s="128" t="n"/>
+      <c r="E12" s="128" t="n"/>
+      <c r="F12" s="128" t="n"/>
+      <c r="G12" s="128" t="n"/>
+      <c r="H12" s="128" t="n"/>
+      <c r="I12" s="128" t="n"/>
+      <c r="J12" s="128" t="n"/>
+      <c r="K12" s="128" t="n"/>
+      <c r="L12" s="128" t="n"/>
+      <c r="M12" s="129" t="n"/>
+    </row>
+    <row r="13" ht="14.1" customHeight="1" s="126">
+      <c r="A13" s="150" t="inlineStr">
         <is>
           <t>VARIABLE</t>
         </is>
       </c>
-      <c r="B13" s="21" t="n"/>
-      <c r="C13" s="45" t="inlineStr">
+      <c r="B13" s="132" t="n"/>
+      <c r="C13" s="151" t="inlineStr">
         <is>
           <t>DESCRIPCIÓN</t>
         </is>
       </c>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="36" t="n"/>
-      <c r="G13" s="36" t="n"/>
-      <c r="H13" s="21" t="n"/>
-      <c r="I13" s="42" t="inlineStr">
+      <c r="D13" s="140" t="n"/>
+      <c r="E13" s="140" t="n"/>
+      <c r="F13" s="140" t="n"/>
+      <c r="G13" s="140" t="n"/>
+      <c r="H13" s="132" t="n"/>
+      <c r="I13" s="152" t="inlineStr">
         <is>
           <t>VALORACIÓN</t>
         </is>
       </c>
-      <c r="J13" s="12" t="n"/>
-      <c r="K13" s="13" t="n"/>
-      <c r="L13" s="44" t="inlineStr">
+      <c r="J13" s="128" t="n"/>
+      <c r="K13" s="129" t="n"/>
+      <c r="L13" s="153" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
-      <c r="M13" s="21" t="n"/>
-    </row>
-    <row r="14" ht="27" customHeight="1" s="19">
-      <c r="A14" s="28" t="n"/>
-      <c r="B14" s="29" t="n"/>
-      <c r="C14" s="28" t="n"/>
-      <c r="D14" s="38" t="n"/>
-      <c r="E14" s="38" t="n"/>
-      <c r="F14" s="38" t="n"/>
-      <c r="G14" s="38" t="n"/>
-      <c r="H14" s="29" t="n"/>
-      <c r="I14" s="47" t="inlineStr">
+      <c r="M13" s="132" t="n"/>
+    </row>
+    <row r="14" ht="27" customHeight="1" s="126">
+      <c r="A14" s="135" t="n"/>
+      <c r="B14" s="136" t="n"/>
+      <c r="C14" s="135" t="n"/>
+      <c r="D14" s="145" t="n"/>
+      <c r="E14" s="145" t="n"/>
+      <c r="F14" s="145" t="n"/>
+      <c r="G14" s="145" t="n"/>
+      <c r="H14" s="136" t="n"/>
+      <c r="I14" s="147" t="inlineStr">
         <is>
           <t>Satisfactorio</t>
         </is>
       </c>
-      <c r="J14" s="13" t="n"/>
-      <c r="K14" s="17" t="inlineStr">
+      <c r="J14" s="129" t="n"/>
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>Por
 mejorar</t>
         </is>
       </c>
-      <c r="L14" s="28" t="n"/>
-      <c r="M14" s="29" t="n"/>
-    </row>
-    <row r="15" ht="38.1" customHeight="1" s="19">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="L14" s="135" t="n"/>
+      <c r="M14" s="136" t="n"/>
+    </row>
+    <row r="15" ht="38.1" customHeight="1" s="126">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>TRANSFERENCIA DE
 CONOCIMIENTO</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="B15" s="129" t="n"/>
+      <c r="C15" s="127" t="inlineStr">
         <is>
           <t>Demuestra    las    competencias    específicas    del programa  de  formación en situaciones reales de trabajo.</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="13" t="n"/>
-      <c r="I15" s="15" t="n"/>
-      <c r="J15" s="13" t="n"/>
-      <c r="K15" s="15" t="n"/>
-      <c r="L15" s="15" t="n"/>
-      <c r="M15" s="13" t="n"/>
-    </row>
-    <row r="16" ht="27" customHeight="1" s="19">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="D15" s="128" t="n"/>
+      <c r="E15" s="128" t="n"/>
+      <c r="F15" s="128" t="n"/>
+      <c r="G15" s="128" t="n"/>
+      <c r="H15" s="129" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="129" t="n"/>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="129" t="n"/>
+    </row>
+    <row r="16" ht="27" customHeight="1" s="126">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>MEJORA
 CONTINUA</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="B16" s="129" t="n"/>
+      <c r="C16" s="127" t="inlineStr">
         <is>
           <t>Aporta  al  mejoramiento de los procesos propios de su desempeño.</t>
         </is>
       </c>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="12" t="n"/>
-      <c r="H16" s="13" t="n"/>
-      <c r="I16" s="15" t="n"/>
-      <c r="J16" s="13" t="n"/>
-      <c r="K16" s="15" t="n"/>
-      <c r="L16" s="15" t="n"/>
-      <c r="M16" s="13" t="n"/>
-    </row>
-    <row r="17" ht="27" customHeight="1" s="19">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="D16" s="128" t="n"/>
+      <c r="E16" s="128" t="n"/>
+      <c r="F16" s="128" t="n"/>
+      <c r="G16" s="128" t="n"/>
+      <c r="H16" s="129" t="n"/>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="129" t="n"/>
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="3" t="n"/>
+      <c r="M16" s="129" t="n"/>
+    </row>
+    <row r="17" ht="27" customHeight="1" s="126">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>FORTALECIMIENTO
 OCUPACIONAL</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="B17" s="129" t="n"/>
+      <c r="C17" s="127" t="inlineStr">
         <is>
           <t>Autogestiona  acciones  que  fortalezca  su  perfil ocupacional en el marco de su proyecto de vida.</t>
         </is>
       </c>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="15" t="n"/>
-      <c r="J17" s="13" t="n"/>
-      <c r="K17" s="15" t="n"/>
-      <c r="L17" s="15" t="n"/>
-      <c r="M17" s="13" t="n"/>
-    </row>
-    <row r="18" ht="33.95" customHeight="1" s="19">
-      <c r="A18" s="47" t="inlineStr">
+      <c r="D17" s="128" t="n"/>
+      <c r="E17" s="128" t="n"/>
+      <c r="F17" s="128" t="n"/>
+      <c r="G17" s="128" t="n"/>
+      <c r="H17" s="129" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="129" t="n"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="129" t="n"/>
+    </row>
+    <row r="18" ht="33.95" customHeight="1" s="126">
+      <c r="A18" s="147" t="inlineStr">
         <is>
           <t>OPORTUNIDAD Y CALIDAD</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="B18" s="129" t="n"/>
+      <c r="C18" s="127" t="inlineStr">
         <is>
           <t>Presenta con oportunidad y calidad los productos generados  en  el  desarrollo  de  sus  funciones  y actividades.</t>
         </is>
       </c>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-      <c r="H18" s="13" t="n"/>
-      <c r="I18" s="15" t="n"/>
-      <c r="J18" s="13" t="n"/>
-      <c r="K18" s="15" t="n"/>
-      <c r="L18" s="15" t="n"/>
-      <c r="M18" s="13" t="n"/>
-    </row>
-    <row r="19" ht="33.95" customHeight="1" s="19">
-      <c r="A19" s="47" t="inlineStr">
+      <c r="D18" s="128" t="n"/>
+      <c r="E18" s="128" t="n"/>
+      <c r="F18" s="128" t="n"/>
+      <c r="G18" s="128" t="n"/>
+      <c r="H18" s="129" t="n"/>
+      <c r="I18" s="3" t="n"/>
+      <c r="J18" s="129" t="n"/>
+      <c r="K18" s="3" t="n"/>
+      <c r="L18" s="3" t="n"/>
+      <c r="M18" s="129" t="n"/>
+    </row>
+    <row r="19" ht="33.95" customHeight="1" s="126">
+      <c r="A19" s="147" t="inlineStr">
         <is>
           <t>RESPONSABILIDAD AMBIENTAL</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="B19" s="129" t="n"/>
+      <c r="C19" s="127" t="inlineStr">
         <is>
           <t>Administra los recursos para el desarrollo de sus actividades    con    criterios    de    responsabilidad ambiental.</t>
         </is>
       </c>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12" t="n"/>
-      <c r="H19" s="13" t="n"/>
-      <c r="I19" s="15" t="n"/>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="15" t="n"/>
-      <c r="L19" s="15" t="n"/>
-      <c r="M19" s="13" t="n"/>
-    </row>
-    <row r="20" ht="33" customHeight="1" s="19">
-      <c r="A20" s="47" t="inlineStr">
+      <c r="D19" s="128" t="n"/>
+      <c r="E19" s="128" t="n"/>
+      <c r="F19" s="128" t="n"/>
+      <c r="G19" s="128" t="n"/>
+      <c r="H19" s="129" t="n"/>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="129" t="n"/>
+      <c r="K19" s="3" t="n"/>
+      <c r="L19" s="3" t="n"/>
+      <c r="M19" s="129" t="n"/>
+    </row>
+    <row r="20" ht="33" customHeight="1" s="126">
+      <c r="A20" s="147" t="inlineStr">
         <is>
           <t>ADMINISTRACIÓN DE RECURSOS</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="B20" s="129" t="n"/>
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Utiliza de manera racional los materiales, equipos y herramientas suministrados para el desempeño
 de sus actividades o funciones.</t>
         </is>
       </c>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12" t="n"/>
-      <c r="G20" s="12" t="n"/>
-      <c r="H20" s="13" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="13" t="n"/>
-      <c r="K20" s="15" t="n"/>
-      <c r="L20" s="15" t="n"/>
-      <c r="M20" s="13" t="n"/>
-    </row>
-    <row r="21" ht="45" customHeight="1" s="19">
-      <c r="A21" s="47" t="inlineStr">
+      <c r="D20" s="128" t="n"/>
+      <c r="E20" s="128" t="n"/>
+      <c r="F20" s="128" t="n"/>
+      <c r="G20" s="128" t="n"/>
+      <c r="H20" s="129" t="n"/>
+      <c r="I20" s="3" t="n"/>
+      <c r="J20" s="129" t="n"/>
+      <c r="K20" s="3" t="n"/>
+      <c r="L20" s="3" t="n"/>
+      <c r="M20" s="129" t="n"/>
+    </row>
+    <row r="21" ht="45" customHeight="1" s="126">
+      <c r="A21" s="147" t="inlineStr">
         <is>
           <t>SEGURIDAD OCUPACIONAL  E INDUSTRIAL</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="B21" s="129" t="n"/>
+      <c r="C21" s="127" t="inlineStr">
         <is>
           <t>Utiliza        los  elementos  de  seguridad  y  salud ocupacional   de   acuerdo   con   la   normatividad vigente    establecida    para    sus    actividades    o funciones.</t>
         </is>
       </c>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="12" t="n"/>
-      <c r="H21" s="13" t="n"/>
-      <c r="I21" s="24" t="n"/>
-      <c r="J21" s="13" t="n"/>
-      <c r="K21" s="24" t="n"/>
-      <c r="L21" s="24" t="n"/>
-      <c r="M21" s="13" t="n"/>
-    </row>
-    <row r="22" ht="39" customHeight="1" s="19">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="D21" s="128" t="n"/>
+      <c r="E21" s="128" t="n"/>
+      <c r="F21" s="128" t="n"/>
+      <c r="G21" s="128" t="n"/>
+      <c r="H21" s="129" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="129" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="129" t="n"/>
+    </row>
+    <row r="22" ht="39" customHeight="1" s="126">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>DOCUMENTACIÓN ETAPA
 PRODUCTIVA</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="B22" s="129" t="n"/>
+      <c r="C22" s="127" t="inlineStr">
         <is>
           <t>Actualiza    permanentemente    el   portafolio   de evidencias.</t>
         </is>
       </c>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="12" t="n"/>
-      <c r="H22" s="13" t="n"/>
-      <c r="I22" s="24" t="n"/>
-      <c r="J22" s="13" t="n"/>
-      <c r="K22" s="24" t="n"/>
-      <c r="L22" s="24" t="n"/>
-      <c r="M22" s="13" t="n"/>
-    </row>
-    <row r="23" ht="13.5" customHeight="1" s="19">
-      <c r="A23" s="57" t="inlineStr">
+      <c r="D22" s="128" t="n"/>
+      <c r="E22" s="128" t="n"/>
+      <c r="F22" s="128" t="n"/>
+      <c r="G22" s="128" t="n"/>
+      <c r="H22" s="129" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="129" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="129" t="n"/>
+    </row>
+    <row r="23" ht="13.5" customHeight="1" s="126">
+      <c r="A23" s="110" t="inlineStr">
         <is>
           <t>Observaciones del responsable ente Coformador.  (</t>
         </is>
       </c>
-      <c r="B23" s="36" t="n"/>
-      <c r="C23" s="36" t="n"/>
-      <c r="D23" s="36" t="n"/>
-      <c r="E23" s="36" t="n"/>
-      <c r="F23" s="36" t="n"/>
-      <c r="G23" s="49" t="inlineStr">
+      <c r="B23" s="140" t="n"/>
+      <c r="C23" s="140" t="n"/>
+      <c r="D23" s="140" t="n"/>
+      <c r="E23" s="140" t="n"/>
+      <c r="F23" s="140" t="n"/>
+      <c r="G23" s="112" t="inlineStr">
         <is>
           <t>Sus observaciones proporcionan información que aporta al</t>
         </is>
       </c>
-      <c r="H23" s="36" t="n"/>
-      <c r="I23" s="36" t="n"/>
-      <c r="J23" s="36" t="n"/>
-      <c r="K23" s="36" t="n"/>
-      <c r="L23" s="36" t="n"/>
+      <c r="H23" s="140" t="n"/>
+      <c r="I23" s="140" t="n"/>
+      <c r="J23" s="140" t="n"/>
+      <c r="K23" s="140" t="n"/>
+      <c r="L23" s="140" t="n"/>
       <c r="M23" s="8" t="n"/>
     </row>
-    <row r="24" ht="13.5" customHeight="1" s="19">
+    <row r="24" ht="13.5" customHeight="1" s="126">
       <c r="A24" s="9" t="n"/>
-      <c r="B24" s="50" t="inlineStr">
+      <c r="B24" s="113" t="inlineStr">
         <is>
           <t>mejoramiento de la calidad de la Formación Profesional Integral</t>
         </is>
       </c>
-      <c r="H24" s="48" t="inlineStr">
+      <c r="H24" s="115" t="inlineStr">
         <is>
           <t>):</t>
         </is>
       </c>
-      <c r="M24" s="27" t="n"/>
-    </row>
-    <row r="25" ht="33.95" customHeight="1" s="19">
-      <c r="A25" s="58" t="n"/>
-      <c r="B25" s="38" t="n"/>
-      <c r="C25" s="38" t="n"/>
-      <c r="D25" s="38" t="n"/>
-      <c r="E25" s="38" t="n"/>
-      <c r="F25" s="38" t="n"/>
-      <c r="G25" s="38" t="n"/>
-      <c r="H25" s="38" t="n"/>
-      <c r="I25" s="38" t="n"/>
-      <c r="J25" s="38" t="n"/>
-      <c r="K25" s="38" t="n"/>
-      <c r="L25" s="38" t="n"/>
-      <c r="M25" s="29" t="n"/>
-    </row>
-    <row r="26" ht="60" customHeight="1" s="19">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="M24" s="134" t="n"/>
+    </row>
+    <row r="25" ht="33.95" customHeight="1" s="126">
+      <c r="A25" s="155" t="n"/>
+      <c r="B25" s="145" t="n"/>
+      <c r="C25" s="145" t="n"/>
+      <c r="D25" s="145" t="n"/>
+      <c r="E25" s="145" t="n"/>
+      <c r="F25" s="145" t="n"/>
+      <c r="G25" s="145" t="n"/>
+      <c r="H25" s="145" t="n"/>
+      <c r="I25" s="145" t="n"/>
+      <c r="J25" s="145" t="n"/>
+      <c r="K25" s="145" t="n"/>
+      <c r="L25" s="145" t="n"/>
+      <c r="M25" s="136" t="n"/>
+    </row>
+    <row r="26" ht="60" customHeight="1" s="126">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Observaciones del Aprendiz:
 4. EVALUACIÓN ETAPA PRODUCTIVA</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="12" t="n"/>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="12" t="n"/>
-      <c r="I26" s="12" t="n"/>
-      <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
-      <c r="L26" s="12" t="n"/>
-      <c r="M26" s="13" t="n"/>
-    </row>
-    <row r="27" ht="14.1" customHeight="1" s="19">
-      <c r="A27" s="51" t="n"/>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="12" t="n"/>
-      <c r="G27" s="12" t="n"/>
-      <c r="H27" s="12" t="n"/>
-      <c r="I27" s="12" t="n"/>
-      <c r="J27" s="12" t="n"/>
-      <c r="K27" s="12" t="n"/>
-      <c r="L27" s="12" t="n"/>
-      <c r="M27" s="13" t="n"/>
-    </row>
-    <row r="28" ht="38.1" customHeight="1" s="19">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="B26" s="128" t="n"/>
+      <c r="C26" s="128" t="n"/>
+      <c r="D26" s="128" t="n"/>
+      <c r="E26" s="128" t="n"/>
+      <c r="F26" s="128" t="n"/>
+      <c r="G26" s="128" t="n"/>
+      <c r="H26" s="128" t="n"/>
+      <c r="I26" s="128" t="n"/>
+      <c r="J26" s="128" t="n"/>
+      <c r="K26" s="128" t="n"/>
+      <c r="L26" s="128" t="n"/>
+      <c r="M26" s="129" t="n"/>
+    </row>
+    <row r="27" ht="14.1" customHeight="1" s="126">
+      <c r="A27" s="156" t="n"/>
+      <c r="B27" s="128" t="n"/>
+      <c r="C27" s="128" t="n"/>
+      <c r="D27" s="128" t="n"/>
+      <c r="E27" s="128" t="n"/>
+      <c r="F27" s="128" t="n"/>
+      <c r="G27" s="128" t="n"/>
+      <c r="H27" s="128" t="n"/>
+      <c r="I27" s="128" t="n"/>
+      <c r="J27" s="128" t="n"/>
+      <c r="K27" s="128" t="n"/>
+      <c r="L27" s="128" t="n"/>
+      <c r="M27" s="129" t="n"/>
+    </row>
+    <row r="28" ht="38.1" customHeight="1" s="126">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>JUICIO DE EVALUACIÓN:                         APROBADO                      NO APROBADO</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="n"/>
-      <c r="G28" s="12" t="n"/>
-      <c r="H28" s="12" t="n"/>
-      <c r="I28" s="12" t="n"/>
-      <c r="J28" s="12" t="n"/>
-      <c r="K28" s="12" t="n"/>
-      <c r="L28" s="12" t="n"/>
-      <c r="M28" s="13" t="n"/>
-    </row>
-    <row r="29" ht="41.1" customHeight="1" s="19">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="B28" s="128" t="n"/>
+      <c r="C28" s="128" t="n"/>
+      <c r="D28" s="128" t="n"/>
+      <c r="E28" s="128" t="n"/>
+      <c r="F28" s="128" t="n"/>
+      <c r="G28" s="128" t="n"/>
+      <c r="H28" s="128" t="n"/>
+      <c r="I28" s="128" t="n"/>
+      <c r="J28" s="128" t="n"/>
+      <c r="K28" s="128" t="n"/>
+      <c r="L28" s="128" t="n"/>
+      <c r="M28" s="129" t="n"/>
+    </row>
+    <row r="29" ht="41.1" customHeight="1" s="126">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>RECONOCIMIENTOS ESPECIALES SOBRE EL DESEMPEÑO: SI                     NO               
 Especificar cuáles:</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="12" t="n"/>
-      <c r="E29" s="12" t="n"/>
-      <c r="F29" s="12" t="n"/>
-      <c r="G29" s="12" t="n"/>
-      <c r="H29" s="12" t="n"/>
-      <c r="I29" s="12" t="n"/>
-      <c r="J29" s="12" t="n"/>
-      <c r="K29" s="12" t="n"/>
-      <c r="L29" s="12" t="n"/>
-      <c r="M29" s="13" t="n"/>
-    </row>
-    <row r="30" ht="48.75" customHeight="1" s="19">
-      <c r="A30" s="54" t="n"/>
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="12" t="n"/>
-      <c r="E30" s="56" t="n"/>
-      <c r="F30" s="36" t="n"/>
-      <c r="G30" s="36" t="n"/>
-      <c r="H30" s="36" t="n"/>
-      <c r="I30" s="36" t="n"/>
-      <c r="J30" s="36" t="n"/>
-      <c r="K30" s="36" t="n"/>
-      <c r="L30" s="36" t="n"/>
-      <c r="M30" s="21" t="n"/>
-    </row>
-    <row r="31" ht="65.25" customHeight="1" s="19">
-      <c r="A31" s="53" t="inlineStr">
+      <c r="B29" s="128" t="n"/>
+      <c r="C29" s="128" t="n"/>
+      <c r="D29" s="128" t="n"/>
+      <c r="E29" s="128" t="n"/>
+      <c r="F29" s="128" t="n"/>
+      <c r="G29" s="128" t="n"/>
+      <c r="H29" s="128" t="n"/>
+      <c r="I29" s="128" t="n"/>
+      <c r="J29" s="128" t="n"/>
+      <c r="K29" s="128" t="n"/>
+      <c r="L29" s="128" t="n"/>
+      <c r="M29" s="129" t="n"/>
+    </row>
+    <row r="30" ht="48.75" customHeight="1" s="126">
+      <c r="A30" s="34" t="n"/>
+      <c r="B30" s="128" t="n"/>
+      <c r="C30" s="128" t="n"/>
+      <c r="D30" s="128" t="n"/>
+      <c r="E30" s="122" t="n"/>
+      <c r="F30" s="140" t="n"/>
+      <c r="G30" s="140" t="n"/>
+      <c r="H30" s="140" t="n"/>
+      <c r="I30" s="140" t="n"/>
+      <c r="J30" s="140" t="n"/>
+      <c r="K30" s="140" t="n"/>
+      <c r="L30" s="140" t="n"/>
+      <c r="M30" s="132" t="n"/>
+    </row>
+    <row r="31" ht="65.25" customHeight="1" s="126">
+      <c r="A31" s="157" t="inlineStr">
         <is>
           <t>Nombre y Firma del ente Coformador                    Firma del Aprendiz                               Nombre y firma Instructor Seguimiento
 Ciudad y fecha de elaboración DIA/MES/AÑO</t>
         </is>
       </c>
-      <c r="B31" s="38" t="n"/>
-      <c r="C31" s="38" t="n"/>
-      <c r="D31" s="38" t="n"/>
-      <c r="E31" s="38" t="n"/>
-      <c r="F31" s="38" t="n"/>
-      <c r="G31" s="38" t="n"/>
-      <c r="H31" s="38" t="n"/>
-      <c r="I31" s="38" t="n"/>
-      <c r="J31" s="38" t="n"/>
-      <c r="K31" s="38" t="n"/>
-      <c r="L31" s="38" t="n"/>
-      <c r="M31" s="29" t="n"/>
+      <c r="B31" s="145" t="n"/>
+      <c r="C31" s="145" t="n"/>
+      <c r="D31" s="145" t="n"/>
+      <c r="E31" s="145" t="n"/>
+      <c r="F31" s="145" t="n"/>
+      <c r="G31" s="145" t="n"/>
+      <c r="H31" s="145" t="n"/>
+      <c r="I31" s="145" t="n"/>
+      <c r="J31" s="145" t="n"/>
+      <c r="K31" s="145" t="n"/>
+      <c r="L31" s="145" t="n"/>
+      <c r="M31" s="136" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="83">
@@ -2255,5 +2645,6 @@
     <mergeCell ref="A20:B20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>